--- a/data/trans_dic/P44-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P44-Provincia-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que se ha realizado alguna vez una prueba para detectar el cancer de colon</t>
+          <t>Población que se ha realizado alguna vez una prueba para detectar el cancer de colon (tasa de respuesta: 98,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,38; 15,99</t>
+          <t>3,53; 15,94</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>16,03; 33,38</t>
+          <t>15,06; 31,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>49,07; 64,18</t>
+          <t>48,57; 63,73</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,03; 18,17</t>
+          <t>5,58; 18,64</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,16; 23,83</t>
+          <t>9,68; 24,07</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,26; 33,09</t>
+          <t>22,55; 32,61</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,75; 15,14</t>
+          <t>6,01; 14,97</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>14,51; 25,11</t>
+          <t>14,23; 25,23</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>36,83; 46,66</t>
+          <t>37,23; 46,74</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,87; 21,53</t>
+          <t>8,82; 21,06</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,84; 9,86</t>
+          <t>2,63; 9,3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25,92; 39,13</t>
+          <t>25,37; 39,31</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,57; 14,53</t>
+          <t>6,02; 14,74</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,27; 5,76</t>
+          <t>0,94; 5,77</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,53; 21,45</t>
+          <t>13,19; 20,81</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,51; 15,65</t>
+          <t>8,24; 15,62</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,41; 6,55</t>
+          <t>2,36; 6,16</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>20,03; 27,96</t>
+          <t>20,34; 27,79</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,48; 15,6</t>
+          <t>3,63; 14,97</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,07; 22,15</t>
+          <t>10,07; 22,19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>30,12; 42,58</t>
+          <t>29,91; 42,88</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,79; 14,36</t>
+          <t>4,86; 15,17</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,0; 18,92</t>
+          <t>7,53; 19,08</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>28,41; 38,97</t>
+          <t>28,79; 39,32</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,71; 12,73</t>
+          <t>5,45; 13,03</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,91; 18,97</t>
+          <t>10,12; 18,26</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>30,85; 39,17</t>
+          <t>30,77; 39,1</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,82; 15,09</t>
+          <t>3,82; 14,78</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,51; 22,74</t>
+          <t>11,33; 23,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>25,28; 37,83</t>
+          <t>24,88; 38,49</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,08; 14,57</t>
+          <t>5,05; 14,5</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,78; 16,92</t>
+          <t>6,88; 16,82</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,36; 35,87</t>
+          <t>26,39; 36,13</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,43; 12,46</t>
+          <t>5,54; 12,45</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,06; 17,75</t>
+          <t>9,82; 17,77</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>27,09; 34,95</t>
+          <t>27,22; 35,12</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,63; 16,28</t>
+          <t>2,79; 15,6</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,11; 9,13</t>
+          <t>1,12; 9,86</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11,68; 23,98</t>
+          <t>10,63; 23,48</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,56; 14,86</t>
+          <t>2,56; 14,87</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,98; 8,57</t>
+          <t>0,98; 9,44</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,87; 17,59</t>
+          <t>9,97; 17,81</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,88; 12,85</t>
+          <t>4,32; 12,45</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,48; 7,06</t>
+          <t>1,54; 7,01</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>11,58; 18,46</t>
+          <t>11,9; 18,5</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4,8; 16,14</t>
+          <t>4,82; 16,6</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,6; 15,74</t>
+          <t>4,59; 16,05</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>23,43; 35,8</t>
+          <t>23,17; 36,33</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,33; 9,95</t>
+          <t>1,65; 9,67</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,99; 12,33</t>
+          <t>2,55; 11,52</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19,07; 28,94</t>
+          <t>18,8; 29,16</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,07; 10,78</t>
+          <t>4,26; 10,97</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4,65; 11,86</t>
+          <t>4,71; 11,61</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>22,9; 30,88</t>
+          <t>22,51; 30,74</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,33; 12,05</t>
+          <t>4,31; 11,85</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>11,7; 20,56</t>
+          <t>11,55; 20,57</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>31,17; 42,43</t>
+          <t>31,35; 42,65</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,98; 12,2</t>
+          <t>4,74; 11,6</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,97; 14,48</t>
+          <t>6,84; 14,82</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,45; 39,86</t>
+          <t>7,62; 39,45</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,36; 10,57</t>
+          <t>5,43; 10,63</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>10,3; 16,62</t>
+          <t>10,16; 15,91</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>12,25; 38,65</t>
+          <t>12,36; 38,93</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>7,34; 15,91</t>
+          <t>7,32; 16,23</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5,53; 12,17</t>
+          <t>5,51; 12,54</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>40,58; 90,3</t>
+          <t>40,63; 89,03</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,33; 7,26</t>
+          <t>2,63; 7,62</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,1; 6,32</t>
+          <t>2,05; 6,31</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>33,22; 41,21</t>
+          <t>32,75; 40,97</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,29; 9,87</t>
+          <t>5,47; 10,0</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>4,08; 7,79</t>
+          <t>4,06; 7,91</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>38,5; 78,11</t>
+          <t>38,13; 76,24</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>7,77; 11,58</t>
+          <t>7,7; 11,57</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>10,13; 13,72</t>
+          <t>10,11; 13,68</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>35,86; 66,53</t>
+          <t>35,77; 65,05</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6,1; 8,95</t>
+          <t>6,23; 9,12</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>6,16; 8,89</t>
+          <t>6,26; 9,09</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>17,47; 30,46</t>
+          <t>16,78; 30,32</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7,3; 9,56</t>
+          <t>7,39; 9,63</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>8,37; 10,58</t>
+          <t>8,5; 10,66</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>29,41; 49,26</t>
+          <t>29,14; 49,69</t>
         </is>
       </c>
     </row>
@@ -1654,7 +1654,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que se ha realizado alguna vez una prueba para detectar el cancer de colon</t>
+          <t>Población que se ha realizado alguna vez una prueba para detectar el cancer de colon (tasa de respuesta: 98,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2892; 13671</t>
+          <t>3015; 13632</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>16903; 35193</t>
+          <t>15882; 33100</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>63576; 83152</t>
+          <t>62929; 82569</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5192; 18767</t>
+          <t>5761; 19245</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>9881; 25708</t>
+          <t>10439; 25968</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>28922; 42999</t>
+          <t>29306; 42368</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10858; 28584</t>
+          <t>11340; 28264</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>30960; 53570</t>
+          <t>30358; 53824</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>95570; 121098</t>
+          <t>96615; 121293</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15337; 37250</t>
+          <t>15263; 36423</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5952; 20648</t>
+          <t>5513; 19482</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>51350; 77518</t>
+          <t>50257; 77862</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11901; 31037</t>
+          <t>12846; 31475</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3069; 13955</t>
+          <t>2287; 13962</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>31737; 50300</t>
+          <t>30941; 48812</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>32879; 60509</t>
+          <t>31853; 60378</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10889; 29577</t>
+          <t>10653; 27804</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>86677; 120968</t>
+          <t>87980; 120238</t>
         </is>
       </c>
     </row>
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5052; 17598</t>
+          <t>4099; 16890</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>14375; 31614</t>
+          <t>14372; 31673</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>47480; 67128</t>
+          <t>47156; 67608</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7139; 21392</t>
+          <t>7237; 22590</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>11131; 30081</t>
+          <t>11963; 30335</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>47017; 64487</t>
+          <t>47649; 65065</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14950; 33319</t>
+          <t>14258; 34102</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>29887; 57212</t>
+          <t>30532; 55093</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>99685; 126561</t>
+          <t>99431; 126348</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5285; 20898</t>
+          <t>5294; 20465</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>18854; 37245</t>
+          <t>18560; 37703</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>42753; 63972</t>
+          <t>42075; 65100</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8102; 23238</t>
+          <t>8050; 23125</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12622; 31479</t>
+          <t>12807; 31292</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>50397; 68585</t>
+          <t>50463; 69093</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>16168; 37121</t>
+          <t>16510; 37089</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>35201; 62102</t>
+          <t>34347; 62168</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>97615; 125930</t>
+          <t>98090; 126537</t>
         </is>
       </c>
     </row>
@@ -2513,47 +2513,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2802; 12567</t>
+          <t>2156; 12042</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>966; 7950</t>
+          <t>974; 8590</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8939; 18350</t>
+          <t>8131; 17963</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3185; 13305</t>
+          <t>2296; 13314</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1049; 9128</t>
+          <t>1040; 10057</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10195; 18160</t>
+          <t>10292; 18388</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6466; 21431</t>
+          <t>7197; 20757</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2860; 13678</t>
+          <t>2982; 13570</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>20826; 33192</t>
+          <t>21392; 33262</t>
         </is>
       </c>
     </row>
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5174; 17391</t>
+          <t>5197; 17889</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5262; 18000</t>
+          <t>5255; 18359</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>31139; 47582</t>
+          <t>30792; 48278</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3028; 12920</t>
+          <t>2136; 12564</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4045; 16657</t>
+          <t>3444; 15565</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>24509; 37195</t>
+          <t>24157; 37475</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9673; 25611</t>
+          <t>10128; 26063</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>11606; 29601</t>
+          <t>11739; 28975</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>59858; 80722</t>
+          <t>58841; 80364</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>10316; 28705</t>
+          <t>10269; 28234</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>30652; 53847</t>
+          <t>30246; 53884</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>91225; 124201</t>
+          <t>91772; 124833</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>14745; 36136</t>
+          <t>14046; 34342</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>20127; 41843</t>
+          <t>19761; 42825</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>37603; 201122</t>
+          <t>38468; 199055</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>28634; 56482</t>
+          <t>29016; 56798</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>56750; 91551</t>
+          <t>55958; 87621</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>97693; 308181</t>
+          <t>98562; 310351</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>19167; 41550</t>
+          <t>19115; 42374</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>17402; 38286</t>
+          <t>17324; 39444</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>224581; 499781</t>
+          <t>224856; 492777</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>7614; 23720</t>
+          <t>8579; 24883</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>7778; 23415</t>
+          <t>7604; 23369</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>116400; 144381</t>
+          <t>114763; 143551</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>31070; 57987</t>
+          <t>32132; 58799</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>27926; 53331</t>
+          <t>27785; 54201</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>347985; 706041</t>
+          <t>344676; 689124</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>92764; 138282</t>
+          <t>91941; 138120</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>141704; 191956</t>
+          <t>141503; 191432</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>613221; 1137669</t>
+          <t>611744; 1112299</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>89516; 131398</t>
+          <t>91432; 133802</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>98308; 141896</t>
+          <t>99931; 145022</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>315898; 550702</t>
+          <t>303346; 548100</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>194216; 254540</t>
+          <t>196684; 256243</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>250835; 316911</t>
+          <t>254479; 319383</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1034627; 1733043</t>
+          <t>1025251; 1748115</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P44-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P44-Provincia-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>56,63%</t>
+          <t>53,11%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>42,02%</t>
+          <t>40,35%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,53; 15,94</t>
+          <t>3,67; 16,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>15,06; 31,4</t>
+          <t>15,66; 32,26</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>48,57; 63,73</t>
+          <t>45,21; 60,52</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,58; 18,64</t>
+          <t>5,6; 19,24</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,68; 24,07</t>
+          <t>9,85; 24,7</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,55; 32,61</t>
+          <t>22,69; 32,81</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,01; 14,97</t>
+          <t>5,91; 14,79</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>14,23; 25,23</t>
+          <t>13,77; 24,78</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>37,23; 46,74</t>
+          <t>35,8; 45,21</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>23,72%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,82; 21,06</t>
+          <t>8,96; 21,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,63; 9,3</t>
+          <t>2,69; 9,14</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25,37; 39,31</t>
+          <t>25,59; 38,45</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,02; 14,74</t>
+          <t>5,99; 14,46</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,94; 5,77</t>
+          <t>0,99; 5,47</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,19; 20,81</t>
+          <t>13,54; 20,94</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,24; 15,62</t>
+          <t>8,26; 15,54</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,36; 6,16</t>
+          <t>2,39; 6,32</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>20,34; 27,79</t>
+          <t>20,24; 27,81</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>35,94%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>35,09%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,63; 14,97</t>
+          <t>3,71; 15,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,07; 22,19</t>
+          <t>9,86; 21,48</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>29,91; 42,88</t>
+          <t>30,18; 42,6</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,86; 15,17</t>
+          <t>4,78; 15,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,53; 19,08</t>
+          <t>7,59; 20,43</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>28,79; 39,32</t>
+          <t>28,76; 39,91</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,45; 13,03</t>
+          <t>5,47; 13,08</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,12; 18,26</t>
+          <t>10,38; 18,97</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>30,77; 39,1</t>
+          <t>31,25; 39,88</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>31,24%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>31,07%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,82; 14,78</t>
+          <t>3,94; 14,31</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,33; 23,01</t>
+          <t>11,33; 23,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>24,88; 38,49</t>
+          <t>25,04; 37,67</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,05; 14,5</t>
+          <t>5,14; 14,66</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,88; 16,82</t>
+          <t>6,4; 17,37</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,39; 36,13</t>
+          <t>26,39; 35,89</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,54; 12,45</t>
+          <t>5,44; 12,66</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,82; 17,77</t>
+          <t>10,38; 17,94</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>27,22; 35,12</t>
+          <t>27,12; 35,09</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,85%</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,79; 15,6</t>
+          <t>3,89; 18,13</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,12; 9,86</t>
+          <t>1,1; 8,14</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,63; 23,48</t>
+          <t>10,99; 23,03</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,56; 14,87</t>
+          <t>3,55; 14,59</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,98; 9,44</t>
+          <t>0,94; 8,69</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,97; 17,81</t>
+          <t>10,05; 18,44</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,32; 12,45</t>
+          <t>3,89; 12,65</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,54; 7,01</t>
+          <t>1,5; 6,98</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>11,9; 18,5</t>
+          <t>11,49; 18,79</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,13%</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4,82; 16,6</t>
+          <t>4,75; 16,68</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,59; 16,05</t>
+          <t>4,87; 17,13</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>23,17; 36,33</t>
+          <t>22,94; 34,81</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,65; 9,67</t>
+          <t>2,32; 9,87</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,55; 11,52</t>
+          <t>3,18; 12,27</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18,8; 29,16</t>
+          <t>18,78; 28,94</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,26; 10,97</t>
+          <t>4,34; 10,97</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4,71; 11,61</t>
+          <t>4,62; 11,43</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>22,51; 30,74</t>
+          <t>22,37; 30,46</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>36,95%</t>
+          <t>37,02%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>37,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>37,4%</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,31; 11,85</t>
+          <t>4,37; 12,51</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>11,55; 20,57</t>
+          <t>11,67; 21,29</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>31,35; 42,65</t>
+          <t>32,07; 42,12</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,74; 11,6</t>
+          <t>4,85; 11,81</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,84; 14,82</t>
+          <t>6,52; 13,99</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,62; 39,45</t>
+          <t>33,83; 42,02</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,43; 10,63</t>
+          <t>5,38; 10,71</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>10,16; 15,91</t>
+          <t>9,89; 16,1</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>12,36; 38,93</t>
+          <t>34,16; 40,64</t>
         </is>
       </c>
     </row>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>67,56%</t>
+          <t>41,29%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>37,13%</t>
+          <t>37,49%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>55,77%</t>
+          <t>39,27%</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>7,32; 16,23</t>
+          <t>7,24; 15,9</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5,51; 12,54</t>
+          <t>5,3; 12,21</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>40,63; 89,03</t>
+          <t>36,18; 45,8</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,63; 7,62</t>
+          <t>2,59; 7,27</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,05; 6,31</t>
+          <t>2,05; 6,27</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>32,75; 40,97</t>
+          <t>33,54; 41,14</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,47; 10,0</t>
+          <t>5,24; 10,02</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>4,06; 7,91</t>
+          <t>4,06; 7,78</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>38,13; 76,24</t>
+          <t>36,17; 42,24</t>
         </is>
       </c>
     </row>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>45,64%</t>
+          <t>36,1%</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>33,04%</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>7,7; 11,57</t>
+          <t>7,78; 11,47</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>10,11; 13,68</t>
+          <t>10,03; 13,54</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>35,77; 65,05</t>
+          <t>33,94; 38,37</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6,23; 9,12</t>
+          <t>6,15; 8,98</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>6,26; 9,09</t>
+          <t>6,16; 8,99</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>16,78; 30,32</t>
+          <t>28,61; 31,9</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7,39; 9,63</t>
+          <t>7,31; 9,67</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>8,5; 10,66</t>
+          <t>8,46; 10,75</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>29,14; 49,69</t>
+          <t>31,62; 34,44</t>
         </is>
       </c>
     </row>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>73367</t>
+          <t>73539</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>35679</t>
+          <t>36670</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>109046</t>
+          <t>110209</t>
         </is>
       </c>
     </row>
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3015; 13632</t>
+          <t>3140; 13950</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>15882; 33100</t>
+          <t>16513; 34016</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>62929; 82569</t>
+          <t>62602; 83794</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5761; 19245</t>
+          <t>5780; 19867</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>10439; 25968</t>
+          <t>10625; 26641</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>29306; 42368</t>
+          <t>30554; 44189</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11340; 28264</t>
+          <t>11157; 27913</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>30358; 53824</t>
+          <t>29370; 52859</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>96615; 121293</t>
+          <t>97765; 123487</t>
         </is>
       </c>
     </row>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>63551</t>
+          <t>66070</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>39517</t>
+          <t>42176</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>103069</t>
+          <t>108247</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15263; 36423</t>
+          <t>15495; 36970</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5513; 19482</t>
+          <t>5633; 19158</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>50257; 77862</t>
+          <t>53442; 80305</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12846; 31475</t>
+          <t>12781; 30881</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2287; 13962</t>
+          <t>2390; 13248</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>30941; 48812</t>
+          <t>33508; 51840</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>31853; 60378</t>
+          <t>31933; 60051</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10653; 27804</t>
+          <t>10777; 28532</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>87980; 120238</t>
+          <t>92373; 126954</t>
         </is>
       </c>
     </row>
@@ -2144,7 +2144,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>56800</t>
+          <t>55642</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>55754</t>
+          <t>57202</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>112555</t>
+          <t>112844</t>
         </is>
       </c>
     </row>
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4099; 16890</t>
+          <t>4181; 17536</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>14372; 31673</t>
+          <t>14069; 30658</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>47156; 67608</t>
+          <t>46724; 65958</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7237; 22590</t>
+          <t>7121; 22344</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>11963; 30335</t>
+          <t>12060; 32478</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>47649; 65065</t>
+          <t>47949; 66555</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14258; 34102</t>
+          <t>14319; 34244</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>30532; 55093</t>
+          <t>31309; 57236</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>99431; 126348</t>
+          <t>100491; 128244</t>
         </is>
       </c>
     </row>
@@ -2307,7 +2307,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>52870</t>
+          <t>59836</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>59177</t>
+          <t>64206</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>112046</t>
+          <t>124042</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5294; 20465</t>
+          <t>5449; 19817</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>18560; 37703</t>
+          <t>18567; 38048</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>42075; 65100</t>
+          <t>47967; 72158</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8050; 23125</t>
+          <t>8194; 23388</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12807; 31292</t>
+          <t>11902; 32318</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>50463; 69093</t>
+          <t>54814; 74532</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>16510; 37089</t>
+          <t>16198; 37720</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>34347; 62168</t>
+          <t>36298; 62752</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>98090; 126537</t>
+          <t>108259; 140088</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12873</t>
+          <t>13519</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13937</t>
+          <t>14745</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>26810</t>
+          <t>28264</t>
         </is>
       </c>
     </row>
@@ -2513,47 +2513,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2156; 12042</t>
+          <t>3004; 13992</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>974; 8590</t>
+          <t>962; 7091</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8131; 17963</t>
+          <t>9020; 18908</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2296; 13314</t>
+          <t>3181; 13070</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1040; 10057</t>
+          <t>997; 9263</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10292; 18388</t>
+          <t>10880; 19967</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7197; 20757</t>
+          <t>6479; 21095</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2982; 13570</t>
+          <t>2913; 13509</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>21392; 33262</t>
+          <t>21882; 35774</t>
         </is>
       </c>
     </row>
@@ -2633,7 +2633,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>38935</t>
+          <t>37837</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>30552</t>
+          <t>31029</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>69487</t>
+          <t>68866</t>
         </is>
       </c>
     </row>
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5197; 17889</t>
+          <t>5122; 17968</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5255; 18359</t>
+          <t>5575; 19600</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>30792; 48278</t>
+          <t>30248; 45904</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2136; 12564</t>
+          <t>3015; 12823</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3444; 15565</t>
+          <t>4290; 16578</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>24157; 37475</t>
+          <t>24741; 38117</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10128; 26063</t>
+          <t>10313; 26058</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>11739; 28975</t>
+          <t>11522; 28523</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>58841; 80364</t>
+          <t>58953; 80276</t>
         </is>
       </c>
     </row>
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>108149</t>
+          <t>124534</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>114700</t>
+          <t>135409</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>222848</t>
+          <t>259944</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>10269; 28234</t>
+          <t>10409; 29812</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>30246; 53884</t>
+          <t>30567; 55762</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>91772; 124833</t>
+          <t>107867; 141682</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>14046; 34342</t>
+          <t>14358; 34979</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>19761; 42825</t>
+          <t>18850; 40410</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>38468; 199055</t>
+          <t>121301; 150680</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>29016; 56798</t>
+          <t>28772; 57248</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>55958; 87621</t>
+          <t>54458; 88690</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>98562; 310351</t>
+          <t>237426; 282461</t>
         </is>
       </c>
     </row>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>373952</t>
+          <t>144487</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>130107</t>
+          <t>148563</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>504059</t>
+          <t>293051</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>19115; 42374</t>
+          <t>18905; 41521</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>17324; 39444</t>
+          <t>16685; 38427</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>224856; 492777</t>
+          <t>126613; 160263</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>8579; 24883</t>
+          <t>8459; 23753</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>7604; 23369</t>
+          <t>7584; 23203</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>114763; 143551</t>
+          <t>132890; 163009</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>32132; 58799</t>
+          <t>30792; 58883</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>27785; 54201</t>
+          <t>27806; 53283</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>344676; 689124</t>
+          <t>269858; 315165</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>780497</t>
+          <t>575464</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>479423</t>
+          <t>530002</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1259920</t>
+          <t>1105467</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>91941; 138120</t>
+          <t>92930; 136953</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>141503; 191432</t>
+          <t>140424; 189496</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>611744; 1112299</t>
+          <t>540928; 611536</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>91432; 133802</t>
+          <t>90234; 131805</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>99931; 145022</t>
+          <t>98230; 143470</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>303346; 548100</t>
+          <t>501033; 558655</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>196684; 256243</t>
+          <t>194689; 257344</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>254479; 319383</t>
+          <t>253370; 322040</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1025251; 1748115</t>
+          <t>1057958; 1152250</t>
         </is>
       </c>
     </row>
